--- a/artfynd/A 11946-2026 artfynd.xlsx
+++ b/artfynd/A 11946-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84254449</v>
+        <v>84254412</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>103691</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>222009</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Sandviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Viola rupestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>F. W. Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84254412</v>
+        <v>84254449</v>
       </c>
       <c r="B3" t="n">
-        <v>103189</v>
+        <v>98050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222009</v>
+        <v>222112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sandviol</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola rupestris</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>F. W. Schmidt</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 11946-2026 artfynd.xlsx
+++ b/artfynd/A 11946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84254412</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84254449</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>